--- a/datos/CuotaCategoria_Directa_2026-08-29.xlsx
+++ b/datos/CuotaCategoria_Directa_2026-08-29.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diego\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DiegoAntonioConstant\Desktop\TrazabilidadSeguimiento\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6104C10-EDB5-41E1-9ACE-3B7F99392C35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB7601B7-979E-4FC6-B943-6F13E5A6B1BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,6 +30,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -873,9 +876,6 @@
       <c r="O3">
         <v>120</v>
       </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
       <c r="Q3" s="12">
         <f>SUM(M3:P3)</f>
         <v>205</v>
@@ -955,7 +955,7 @@
         <v>0</v>
       </c>
       <c r="Q4" s="12">
-        <f t="shared" ref="Q3:Q14" si="8">SUM(M4:O4)</f>
+        <f t="shared" ref="Q4:Q14" si="8">SUM(M4:O4)</f>
         <v>105</v>
       </c>
       <c r="R4" s="13">
@@ -1027,18 +1027,18 @@
         <v>35</v>
       </c>
       <c r="O5">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5" s="12">
         <f t="shared" si="8"/>
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="R5" s="13">
         <f t="shared" si="4"/>
-        <v>4.166666666666667</v>
+        <v>3.625</v>
       </c>
       <c r="S5" t="str">
         <f t="shared" si="5"/>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="U5" s="12">
         <f t="shared" si="6"/>
-        <v>50</v>
+        <v>43.5</v>
       </c>
       <c r="V5" s="12">
         <f t="shared" si="7"/>
@@ -1099,7 +1099,7 @@
         <v>3.3000000000000003</v>
       </c>
       <c r="M6">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="N6">
         <v>35</v>
@@ -1112,11 +1112,11 @@
       </c>
       <c r="Q6" s="12">
         <f t="shared" si="8"/>
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="R6" s="13">
         <f t="shared" si="4"/>
-        <v>23.5</v>
+        <v>18.5</v>
       </c>
       <c r="S6" t="str">
         <f t="shared" si="5"/>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="U6" s="12">
         <f t="shared" si="6"/>
-        <v>70.5</v>
+        <v>55.5</v>
       </c>
       <c r="V6" s="12">
         <f t="shared" si="7"/>
@@ -1177,7 +1177,7 @@
         <v>92.4</v>
       </c>
       <c r="M7">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="N7">
         <v>35</v>
@@ -1190,11 +1190,11 @@
       </c>
       <c r="Q7" s="12">
         <f t="shared" si="8"/>
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="R7" s="13">
         <f t="shared" si="4"/>
-        <v>2.0476190476190474</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="S7" t="str">
         <f t="shared" si="5"/>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="U7" s="12">
         <f t="shared" si="6"/>
-        <v>172</v>
+        <v>112</v>
       </c>
       <c r="V7" s="12">
         <f t="shared" si="7"/>
@@ -1339,18 +1339,18 @@
         <v>35</v>
       </c>
       <c r="O9">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9" s="12">
         <f t="shared" si="8"/>
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="R9" s="13">
         <f t="shared" si="4"/>
-        <v>1.7419354838709677</v>
+        <v>1.403225806451613</v>
       </c>
       <c r="S9" t="str">
         <f t="shared" si="5"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M15" s="15">
         <f t="shared" si="9"/>
-        <v>600</v>
+        <v>540</v>
       </c>
       <c r="N15" s="15">
         <f t="shared" si="9"/>
@@ -1801,19 +1801,19 @@
       </c>
       <c r="O15" s="15">
         <f t="shared" si="9"/>
-        <v>362</v>
+        <v>328</v>
       </c>
       <c r="Q15" s="15">
         <f>SUBTOTAL(9,Q3:Q14)</f>
-        <v>1379</v>
+        <v>1285</v>
       </c>
       <c r="R15" s="16">
         <f t="shared" si="4"/>
-        <v>1.6920245398773006</v>
+        <v>1.5766871165644172</v>
       </c>
       <c r="U15" s="15">
         <f>SUBTOTAL(9,U3:U14)</f>
-        <v>365.65</v>
+        <v>284.14999999999998</v>
       </c>
       <c r="V15" s="15">
         <f>SUBTOTAL(9,V3:V14)</f>
@@ -1873,11 +1873,11 @@
       </c>
       <c r="D4" s="12">
         <f>SUMIF('CUOTA CLIENTE - CATEGORÍA'!$B$3:$B$14,B4,'CUOTA CLIENTE - CATEGORÍA'!$Q$3:$Q$14)</f>
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="E4" s="13">
         <f>IFERROR(D4/C4,0)</f>
-        <v>2.5786163522012577</v>
+        <v>2.4968553459119498</v>
       </c>
       <c r="F4" t="str">
         <f>IF(E4&gt;=99.99%,"GANA","NO GANA")</f>
@@ -1897,11 +1897,11 @@
       </c>
       <c r="D5" s="12">
         <f>SUMIF('CUOTA CLIENTE - CATEGORÍA'!$B$3:$B$14,B5,'CUOTA CLIENTE - CATEGORÍA'!$Q$3:$Q$14)</f>
-        <v>314</v>
+        <v>254</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(D5/C5,0)</f>
-        <v>4.3611111111111107</v>
+        <v>3.5277777777777777</v>
       </c>
       <c r="F5" t="str">
         <f>IF(E5&gt;=99.99%,"GANA","NO GANA")</f>
@@ -1921,11 +1921,11 @@
       </c>
       <c r="D6" s="12">
         <f>SUMIF('CUOTA CLIENTE - CATEGORÍA'!$B$3:$B$14,B6,'CUOTA CLIENTE - CATEGORÍA'!$Q$3:$Q$14)</f>
-        <v>325</v>
+        <v>304</v>
       </c>
       <c r="E6" s="13">
         <f>IFERROR(D6/C6,0)</f>
-        <v>0.72383073496659245</v>
+        <v>0.6770601336302895</v>
       </c>
       <c r="F6" t="str">
         <f>IF(E6&gt;=99.99%,"GANA","NO GANA")</f>
